--- a/assets/docs/puestos.xlsx
+++ b/assets/docs/puestos.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB51FD6-7A6E-46D3-B32D-4AE57F59BDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1537A8C0-74F6-4DFE-BDB3-DB2FD0E2D475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
   </bookViews>
   <sheets>
     <sheet name="Puestos" sheetId="1" r:id="rId1"/>
+    <sheet name="CATEGORIA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,12 +33,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>PUESTO</t>
   </si>
   <si>
     <t>DEPARTAMENTO</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>CONFIANZA</t>
+  </si>
+  <si>
+    <t>HONORARIOS</t>
+  </si>
+  <si>
+    <t>EVENTUAL</t>
+  </si>
+  <si>
+    <t>SINDICALIZADO</t>
+  </si>
+  <si>
+    <t>DIETAS</t>
   </si>
 </sst>
 </file>
@@ -413,22 +435,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF703789-3435-4D03-ABEF-93E46EBDB414}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{90D1058E-9C69-419C-A3D7-189C6D75FE02}">
+          <x14:formula1>
+            <xm:f>CATEGORIA!$A$1:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC575C18-58E1-4BBB-975B-1B0E4065CF48}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>